--- a/paper/revision/reviewer_response_tracker.xlsx
+++ b/paper/revision/reviewer_response_tracker.xlsx
@@ -1041,22 +1041,22 @@
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>Rerun the influencer exclusion using the top 1, 5, and 10 percent most-followed accounts on both platforms and show the results hold; keep the original cutoff as one specification.</t>
+          <t>Push back with evidence rather than rerun. Our data show Truth Social has a separated influencer class that Bluesky lacks: the top TS account has 56 times the followers of the platform's 99.9th percentile account (Bluesky: 5 times), the top 8 TS accounts hold 16 percent of all follower ties (Bluesky: 6 percent), and TS's 8th account outranks Bluesky's 1st. A symmetric top-n-percent rule would remove ordinary accounts on one platform to mirror an anomaly on the other. Add these numbers to the appendix next to the follower CCDF.</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>Yes, small</t>
+          <t>Done (distribution stats computed)</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Response paragraph drafted; appendix numbers ready</t>
         </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>Half a day</t>
+          <t>Add the statistics to the appendix text</t>
         </is>
       </c>
     </row>

--- a/paper/revision/reviewer_response_tracker.xlsx
+++ b/paper/revision/reviewer_response_tracker.xlsx
@@ -1041,7 +1041,7 @@
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>Push back with evidence rather than rerun. Our data show Truth Social has a separated influencer class that Bluesky lacks: the top TS account has 56 times the followers of the platform's 99.9th percentile account (Bluesky: 5 times), the top 8 TS accounts hold 16 percent of all follower ties (Bluesky: 6 percent), and TS's 8th account outranks Bluesky's 1st. A symmetric top-n-percent rule would remove ordinary accounts on one platform to mirror an anomaly on the other. Add these numbers to the appendix next to the follower CCDF.</t>
+          <t>The reviewer suggests excluding the top n percent of accounts on both platforms instead of only Truth Social. We push back with evidence rather than rerun the analysis. Our data show the two platforms' follower distributions are not comparable at the top. The largest Truth Social account (Trump, 7.1M followers) has 56 times the followers of the platform's own 99.9th percentile account, and the top 8 accounts hold 16 percent of all followers in our data. On Bluesky the largest account is only 5 times above the 99.9th percentile, and the top 8 hold 6 percent. Even the 8th largest Truth Social account is bigger than the largest Bluesky account. In short, Truth Social has a separated class of dominant accounts and Bluesky does not, so a symmetric top n percent rule would remove ordinary Bluesky accounts just to mirror something that only exists on Truth Social. We will add these numbers to the appendix next to the follower CCDF and explain this in the response letter.</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">

--- a/paper/revision/reviewer_response_tracker.xlsx
+++ b/paper/revision/reviewer_response_tracker.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Repost cascades are reconstructed, not observed. The similarity between platforms could be an artifact of the reconstruction method. Validate it or drop reposts.</t>
+          <t>True repost paths are not observed, so we rebuild them by linking each repost to an earlier reposter the user follows. Reviewers worry that our choice of LINKING RULE could itself create the cross-platform similarity, and ask us to validate it or drop the repost analysis.</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>A user may have followed someone only after reposting, so inferred paths could be wrong. Could this error differ between platforms?</t>
+          <t>Different from C1: here the concern is the FOLLOW NETWORK we link with, not the linking rule. We collected who-follows-whom after the fact, so a follow edge we rely on may have been created only after the repost happened. R3 asks us to discuss this error and whether it differs between platforms.</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>Our follow networks have no timestamps, so we cannot check follow dates directly. We will add a sensitivity check that randomly deletes 5 to 30 percent of follow edges and shows the results hold, plus an honest limitation sentence noting the platform asymmetry in data collection.</t>
+          <t>Neither platform provides follow dates, so we cannot check the timing directly. We will run a sensitivity check that randomly deletes 5 to 30 percent of follow edges, simulating follows that did not exist yet at repost time, and show the results hold. We will also note the error has a known direction (a spurious follow edge can only move a repost from the root to deeper in the tree, a case already bounded by the C1 checks) and add a limitation sentence about the different crawl times of the two follow networks.</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">

--- a/paper/revision/reviewer_response_tracker.xlsx
+++ b/paper/revision/reviewer_response_tracker.xlsx
@@ -715,12 +715,12 @@
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>Confusion matrices ready; simulation not started</t>
+          <t>DONE. All 100 draws under measured per-platform noise keep at least 83 percent of the platform gap absorbed (median 95 percent); a cruder pooled stress test still absorbs about two thirds. See results/noise_propagation/RESULTS.md</t>
         </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>1 to 2 days</t>
+          <t>Write the appendix paragraph and add the summary table</t>
         </is>
       </c>
     </row>

--- a/paper/revision/reviewer_response_tracker.xlsx
+++ b/paper/revision/reviewer_response_tracker.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Status (Aug 17)</t>
+          <t>Status (Aug 18)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>We rebuilt every repost cascade under 5 alternative linking rules plus a 40-draw random rule ensemble, on the full data (244k cascades, 4M reposts). The platform difference stays near zero (within +/-0.03) under every rule, while the reply difference is 5 to 8 times larger. So the finding is not an artifact. We will also rename these cascades 'reconstructed' and align the code with the rule described in the appendix.</t>
+          <t>Written into the revision (new appendix section + Figure 5)</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
@@ -505,12 +505,12 @@
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>Analysis complete; results and draft figure ready</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>Write the new appendix section and add the figure</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>Clarify in the text: reply cascade nodes are posts (a user replying twice appears twice); repost nodes are individual reposts. Add a check where we collapse repeated users and show depth and breadth conclusions do not change.</t>
+          <t>Nodes are posts; stated explicitly. Rebuilt all reply trees and recomputed metrics both post-level and user-collapsed. Post-level reproduces the analysis file (r=0.999). Under user-collapsing the depth gap holds but the breadth gap is much smaller, so part of the raw breadth difference is repeat posting by the same Truth Social users rather than more distinct participants. We report both, and correct the submitted appendix which wrongly described size as a count of unique users.</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
@@ -589,12 +589,12 @@
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done (analysis + text)</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>1 day: clarification text plus the user-collapsed recomputation</t>
+          <t>Written</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>Define center explicitly in the text (it is a residual: users below the left or right threshold) and rerun the main models excluding center users to show the conclusions hold.</t>
+          <t>Center is defined in the text as a residual category. Refit with composition and alignment over partisan users only: ideology still absorbs 61 percent of the breadth gap and 64 percent of the depth gap, versus 99 and 77 percent under the published specification. Weaker but not reversed; both reported.</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
@@ -673,12 +673,12 @@
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>Half a day</t>
+          <t>Written</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>Use the measured confusion matrix to simulate label errors at the observed rates, rerun the composition and alignment models, and show the conclusions are stable. The measured errors go in the direction R1 suspected (model over-assigns left on TS and right on Bluesky), so this directly answers him with numbers.</t>
+          <t>All 100 draws under measured per-platform noise keep at least 83 percent of the platform gap absorbed (median 95 percent); a pooled stress test still absorbs about two thirds. Written into the appendix.</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr">
@@ -715,12 +715,12 @@
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>DONE. All 100 draws under measured per-platform noise keep at least 83 percent of the platform gap absorbed (median 95 percent); a cruder pooled stress test still absorbs about two thirds. See results/noise_propagation/RESULTS.md</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>Write the appendix paragraph and add the summary table</t>
+          <t>Written</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>Add a paragraph: our sample is Biden/Trump-mention activity during the campaign, not the whole platform, so the mix should differ from platform-wide estimates. Pair it with noise-corrected prevalence estimates from C6.</t>
+          <t>Prevalence correction using the measured confusion matrix lowers our Bluesky right share from 24.2 to 6.9 percent, close to the 4.8 percent Quelle and Bovet report platform-wide. Paired with an explanation of why a candidate-mention sample differs from a platform-wide one. Citation updated to the published PLOS ONE version, plus a newer Bluesky study added.</t>
         </is>
       </c>
       <c r="F8" s="1" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>Half a day of writing once C6 is done</t>
+          <t>Written</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>Replace 'explains' with 'is associated with' or 'statistically accounts for' throughout, and add a paragraph discussing the two-way relationship (deep versus star-shaped cascades offer different chances for cross-ideology contact).</t>
+          <t>Causal language replaced with statistical accounting throughout Results and Discussion, plus a new paragraph stating the endogeneity in the reviewers own terms and naming the early-cascade design as future work rather than implying we ran it.</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>1 day of careful editing; optional extra analysis predicting final shape from early-cascade alignment only</t>
+          <t>Written</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>Add a descriptive table: posts, users, cascades, and cascade counts by size bin, per platform and cascade type.</t>
+          <t>Descriptive statistics table added (cascades, messages, size bands by platform and cascade type).</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
@@ -841,12 +841,12 @@
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>Half a day</t>
+          <t>Written</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>Add a table of raw counts next to the z-scores. The counts already exist as pipeline output files.</t>
+          <t>Full table of raw counts for all 54 ideology-labeled motifs on both platforms.</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>Half a day</t>
+          <t>Written</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>Explain in the text: the null model randomizes and recounts the same way, so overlapping motifs occur in both the observed and randomized graphs and the z-scores compare like with like. State the randomization procedure precisely.</t>
+          <t>Null model described precisely from the source code (within-cascade degree-preserving edge swaps, 100 randomizations). Overlap does not bias z-scores because null graphs use the identical enumeration; the real consequence, correlated z-scores across neighbouring motifs, is now stated.</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>A paragraph</t>
+          <t>Written</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>The code uses robust regression (Huber). The appendix paragraph is leftover from an earlier version and will be rewritten. We also found a technical issue while checking: standard robust regression breaks on repost cascades because most are tiny, which we now document and handle.</t>
+          <t>Appendix corrected to describe the Huber estimator actually used. While checking, found the robust regression scale estimate collapses because 61 percent of reply cascades are single posts sitting at the origin; added a sensitivity table across two samples and two scale estimators, where ideology absorbs 81 to 94 percent of the gap in all eight combinations.</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
@@ -967,12 +967,12 @@
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>Diagnosed; text not fixed yet</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>A paragraph plus re-verifying the reported numbers</t>
+          <t>Written</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>Rewrite the discussion: state what we claim generalizes (structural signatures of ideologically sorted versus mixed platforms) versus what is context-bound, and spell out the practical meaning of the two conversation shapes.</t>
+          <t>Discussion now says what wide-shallow versus narrow-deep means for how attention is distributed, plus a methodological implication. Limitations separate what generalizes from what is bound to this election context.</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>1 to 2 days of writing</t>
+          <t>Written</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>Count the share of reply chains that alternate between the same two accounts, per platform, and report it.</t>
+          <t>Among cascades deep enough to permit it, two-user exchanges appear in 68.8 percent of Bluesky and 70.0 percent of Truth Social cascades, so the depth difference is not explained by dyadic ping-pong.</t>
         </is>
       </c>
       <c r="F16" s="1" t="inlineStr">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>A short script</t>
+          <t>Written</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>Report corpus sizes, the outlier share, topic counts, and example topics per platform. The numbers exist in the saved model outputs.</t>
+          <t>Reported corpus size (125,602 posts), the outlier reduction step, the resulting 0.02 percent outlier share, topic counts and largest topics, and the trade-off outlier reduction involves.</t>
         </is>
       </c>
       <c r="F17" s="1" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>Half a day</t>
+          <t>Written</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>Rewrite that subsection with a worked example and a plain definition of alignment ratio; define all notation at first use.</t>
+          <t>Worked example added where alignment is defined, plus a plain statement that alignment is a property of the conversation not of a participant.</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>Half a day</t>
+          <t>Written</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>Add 2023 to 2026 papers on cascades and newer platforms, including the Bovet team's Bluesky paper.</t>
+          <t>Updated the Bluesky ideology citation to its published PLOS ONE version and added a 2025 Bluesky politics paper. A broader refresh would benefit from Mao naming specific recent work; the response letter also invites the reviewer to suggest papers.</t>
         </is>
       </c>
       <c r="F20" s="1" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Partly done</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>Half a day</t>
+          <t>Optional further additions</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>Acknowledge in limitations; note non-US extension as future work. No analysis change.</t>
+          <t>US-centric scope acknowledged in limitations with non-US replication named as the next step.</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>One sentence</t>
+          <t>Written</t>
         </is>
       </c>
     </row>

--- a/paper/revision/reviewer_response_tracker.xlsx
+++ b/paper/revision/reviewer_response_tracker.xlsx
@@ -537,22 +537,22 @@
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>Neither platform provides follow dates, so we cannot check the timing directly. We will run a sensitivity check that randomly deletes 5 to 30 percent of follow edges, simulating follows that did not exist yet at repost time, and show the results hold. We will also note the error has a known direction (a spurious follow edge can only move a repost from the root to deeper in the tree, a case already bounded by the C1 checks) and add a limitation sentence about the different crawl times of the two follow networks.</t>
+          <t>Neither platform exposes follow creation dates, so we cannot verify timing directly. We bound the consequence two ways. The error has a known direction: a follow that did not yet exist can only move a repost from the root to an interior parent, a displacement already covered by the alternative rules in C1. And we ran a direct test, deleting follow edges at random at 5 to 30 percent and re-estimating: the breadth interaction moves from 0.031 to 0.005 and depth from 0.004 to 0.013, both far below the reply values of 0.170 and -0.182. We also state that the error may be asymmetric, since the two follow networks were crawled at different times and Truth Social accounts have larger followee sets.</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>Yes, small</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>Half a day: one loop over the existing robustness code</t>
+          <t>Written</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>Quality pass on every figure: labels, overlap, axis titles, consistent fonts and resolution.</t>
+          <t>Audited all 12 figures: every one is at or above 300 dpi, so resolution is fine. The real issue is in the two motif figures, where the family labels (Aligned, End shift, Mid shift, Diverse) are drawn as watermarks inside the plot and sit on top of the data, and where two families both show alignment = 0.00, which reads as an error. We clarified both captions now. Moving the labels above the axes requires re-running the notebook cell that builds the figure, which is the one presentation item still outstanding.</t>
         </is>
       </c>
       <c r="F19" s="1" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Partly done (captions fixed; layout needs a notebook rerun)</t>
         </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>1 to 2 days</t>
+          <t>Half a day, needs the notebook environment</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>Notation pass (define at first use) and fix the indentation.</t>
+          <t>Fixed the stray indent (a blank line after display math started a new paragraph). Notation defined at first use in the revised sections.</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>Hours</t>
+          <t>Written</t>
         </is>
       </c>
     </row>

--- a/paper/revision/reviewer_response_tracker.xlsx
+++ b/paper/revision/reviewer_response_tracker.xlsx
@@ -1051,12 +1051,12 @@
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>Response paragraph drafted; appendix numbers ready</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>Add the statistics to the appendix text</t>
+          <t>Written (appendix reports the distribution statistics; response paragraph drafted)</t>
         </is>
       </c>
     </row>

--- a/paper/revision/reviewer_response_tracker.xlsx
+++ b/paper/revision/reviewer_response_tracker.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Status (Aug 18)</t>
+          <t>Status (Aug 24)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -621,22 +621,22 @@
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>Found the validation file and computed everything: per-class and per-platform precision and recall, confusion matrices, agreement. Human agreement is strong (kappa 0.89). Remaining decision: two cells are thin (9 items for right-on-Bluesky, 19 for center-on-TS). Preferred fix is a small top-up: Mao and Chen each code about 170 more items (about 2 hours each). Fallback: report confidence intervals and rely on the pooled noise analysis. No new coder needed either way.</t>
+          <t>Recomputed from the canonical file src/val_ideology.csv (an earlier run used a superseded copy whose second annotator differed on 15 items). Report per-class and per-platform precision and recall with percentile bootstrap 95 percent intervals over 2,000 resamples, plus overall accuracy 0.86 and inter-annotator kappa 0.77 [0.70, 0.85]. Per Ceren, we do NOT stratify-upsample the rare classes, since that invites the objection that the validation set was built to look good. The bootstrap shows exactly where the evidence is thin: pooled and majority-class rates are tight; right-on-Bluesky rests on 8 items with an interval of 0.33 to 0.91. Plan is to add a modest amount of unstratified annotation and show the rates do not move.</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>Done in part</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>Metrics computed; top-up decision open</t>
+          <t>Done (bootstrap reported); modest unstratified top-up planned</t>
         </is>
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>Top-up: 2 hours per coder plus a rerun of the script</t>
+          <t>Optional: some more annotation, unstratified, to show rates are stable</t>
         </is>
       </c>
     </row>

--- a/paper/revision/reviewer_response_tracker.xlsx
+++ b/paper/revision/reviewer_response_tracker.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Status (Aug 24)</t>
+          <t>Status (Aug 30)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>Recomputed from the canonical file src/val_ideology.csv (an earlier run used a superseded copy whose second annotator differed on 15 items). Report per-class and per-platform precision and recall with percentile bootstrap 95 percent intervals over 2,000 resamples, plus overall accuracy 0.86 and inter-annotator kappa 0.77 [0.70, 0.85]. Per Ceren, we do NOT stratify-upsample the rare classes, since that invites the objection that the validation set was built to look good. The bootstrap shows exactly where the evidence is thin: pooled and majority-class rates are tight; right-on-Bluesky rests on 8 items with an interval of 0.33 to 0.91. Plan is to add a modest amount of unstratified annotation and show the rates do not move.</t>
+          <t>Defend the sample we have; collect nothing new. Every rate carries a percentile bootstrap interval, so a reader sees which cells are solid (pooled and majority classes) and which are thin (right-on-Bluesky, 8 items, 0.33 to 0.91). Three checks then establish what the sample does support: (a) the directional claim, that each platform's minority is over-assigned, is significant on both platforms (p = 0.017 and 0.004); (b) the pattern is unchanged whether we score against Annotator 1, Annotator 2, or consensus, and we adopt the harsher single-annotator rates as a worst case; (c) user labels aggregate multiple posts, so user-level accuracy (0.87 to 0.88) exceeds the post-level accuracy we validate (0.81 to 0.85), making the noise analysis conservative. Most directly, the noise analysis now includes a nested bootstrap that resamples the validation set itself, carrying its uncertainty into the substantive result.</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
@@ -631,12 +631,12 @@
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>Done (bootstrap reported); modest unstratified top-up planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>Optional: some more annotation, unstratified, to show rates are stable</t>
+          <t>Written</t>
         </is>
       </c>
     </row>

--- a/paper/revision/reviewer_response_tracker.xlsx
+++ b/paper/revision/reviewer_response_tracker.xlsx
@@ -957,7 +957,7 @@
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>Appendix corrected to describe the Huber estimator actually used. While checking, found the robust regression scale estimate collapses because 61 percent of reply cascades are single posts sitting at the origin; added a sensitivity table across two samples and two scale estimators, where ideology absorbs 81 to 94 percent of the gap in all eight combinations.</t>
+          <t>Appendix corrected to describe the Huber estimator actually used. Re-estimating exposed that the submitted Table 1 was fitted with the default MAD scale, which degenerates here (scale 1e-14 to 6e-18), so its standard errors and significance stars could not be interpreted. Table 1 is rebuilt under Huber proposal 2 with real standard errors and the estimator stated. Model 3c breadth moves 0.023 to 0.071 against a baseline of 0.419, so the text now reports a five-sixths reduction instead of 'close to zero'. Two further errors found and corrected: Model 2's footnote misdescribed a three-level platform variable as an outlier interaction, and Model 4's breadth coefficient disagreed with its own fit statistics while its depth row did not reproduce.</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">

--- a/paper/revision/reviewer_response_tracker.xlsx
+++ b/paper/revision/reviewer_response_tracker.xlsx
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>Audited all 12 figures: every one is at or above 300 dpi, so resolution is fine. The real issue is in the two motif figures, where the family labels (Aligned, End shift, Mid shift, Diverse) are drawn as watermarks inside the plot and sit on top of the data, and where two families both show alignment = 0.00, which reads as an error. We clarified both captions now. Moving the labels above the axes requires re-running the notebook cell that builds the figure, which is the one presentation item still outstanding.</t>
+          <t>Audited all 12 figures: every one is at or above 300 dpi. The substantive defect was in the two motif figures, where the family labels were drawn as watermarks inside the panel and sat on top of the data. Both figures are rebuilt with the labels in a header band above the axes, from a standalone script that reads the motif pipeline's z-score files, so they no longer depend on notebook state. Data, ordering, palette and thresholds unchanged; values spot-checked against the source files. Captions updated to match.</t>
         </is>
       </c>
       <c r="F19" s="1" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>Partly done (captions fixed; layout needs a notebook rerun)</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>Half a day, needs the notebook environment</t>
+          <t>Written</t>
         </is>
       </c>
     </row>

--- a/paper/revision/reviewer_response_tracker.xlsx
+++ b/paper/revision/reviewer_response_tracker.xlsx
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>Updated the Bluesky ideology citation to its published PLOS ONE version and added a 2025 Bluesky politics paper. A broader refresh would benefit from Mao naming specific recent work; the response letter also invites the reviewer to suggest papers.</t>
+          <t>Added ten recent works (2024-2025), each integrated where it does argumentative work rather than appended as a block, and every one verified against a fetched page or Crossref before citing. Most consequential: DeVerna et al. 2024 on the cascade inference problem, which formalises the exact worry reviewers raised about reconstructed repost trees and studies Bluesky; we cite it at the reconstruction and in the robustness appendix, and frame our rule-envelope analysis as the response. Also added Gonzalez-Bailon et al. 2024 and Slaughter et al. 2025 (depth/breadth framework in current use), Niitsuma et al. 2025 (influencer concentration; also upgraded from the preprint we already cited to the published Scientific Reports version), Nogara et al. 2025 and Shah et al. 2024 (platform context; Nogara gives a second independent Bluesky composition estimate of 7.2 percent right-leaning), Quelle et al. 2025 (migration as contagion, supporting the self-selection reading), and TeBlunthuis et al. 2024, Egami et al. 2023, Vallejo Vera and Driggers 2025 on label error propagating into downstream regression and on LLM reliability varying by political position.</t>
         </is>
       </c>
       <c r="F20" s="1" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>Partly done</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>Optional further additions</t>
+          <t>Written</t>
         </is>
       </c>
     </row>

--- a/paper/revision/reviewer_response_tracker.xlsx
+++ b/paper/revision/reviewer_response_tracker.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>Our follow networks have no timestamps, so we cannot check follow dates directly (but one point I will make is that the collection is at the same time, so not really far apart). We will add a sensitivity check that randomly deletes 5 to 30 percent of follow edges and shows the results hold, plus an limitation sentence noting the platform asymmetry in data collection.</t>
+          <t>Our follow networks have no timestamps, so we cannot check follow dates directly (but one point I will make is that the collection is at the same time, so not really far apart). We will add a sensitivity check that randomly deletes 5 to 30 percent of follow edges and shows the results hold, plus a sentence noting that both follow networks were collected at the same time, so the timing gap is the same for both platforms.</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">

--- a/paper/revision/reviewer_response_tracker.xlsx
+++ b/paper/revision/reviewer_response_tracker.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>Clarify in the text: reply cascade nodes are posts, while ideology is aggregated at the user level, so each node carries its author's user-level label and a user who replies twice appears twice. Repost nodes are individual reposts. We also add a check that collapses repeated users into one node. The depth conclusion holds, but the breadth gap shrinks substantially (baseline 0.168 at post level against -0.032 collapsed), which says part of Truth Social's extra width is the same users posting repeatedly rather than more distinct participants. We report both representations.</t>
+          <t>Clarify in the text: reply cascade nodes are posts, while ideology is aggregated at the user level, so each node carries its author's user-level label and a user who replies twice appears twice. Repost nodes are individual reposts. We also add a check that collapses repeated users into one node. The depth conclusion holds, but the breadth gap shrinks substantially (within the cascades that contain a reply, baseline 0.168 at post level against -0.032 collapsed; not comparable to Table 1's 0.419, which is estimated on all cascades including single posts), which says part of Truth Social's extra width is the same users posting repeatedly rather than more distinct participants. We report both representations.</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">

--- a/paper/revision/reviewer_response_tracker.xlsx
+++ b/paper/revision/reviewer_response_tracker.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>Clarify in the text: reply cascade nodes are posts, while ideology is aggregated at the user level, so each node carries its author's user-level label and a user who replies twice appears twice. Repost nodes are individual reposts. We also add a check that collapses repeated users into one node. The depth conclusion holds, but the breadth gap shrinks substantially (within the cascades that contain a reply, baseline 0.168 at post level against -0.032 collapsed; not comparable to Table 1's 0.419, which is estimated on all cascades including single posts), which says part of Truth Social's extra width is the same users posting repeatedly rather than more distinct participants. We report both representations.</t>
+          <t>Clarify in the text: reply cascade nodes are posts, while ideology is aggregated at the user level, so each node carries its author's user-level label and a user who replies twice appears twice. Repost nodes are individual reposts. We also add a check that collapses repeated users into one node. The depth conclusion holds, but the breadth gap shrinks substantially (on the same 42,947 threads, baseline 0.160 at post level against -0.032 collapsed; not comparable to Table 1's 0.419, which is estimated on all cascades including single posts), which says part of Truth Social's extra width is the same users posting repeatedly rather than more distinct participants. We report both representations.</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
